--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2016_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>90</t>
+    <t>86</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>5.378</t>
-  </si>
-  <si>
-    <t>(3.473)</t>
-  </si>
-  <si>
-    <t>6.789</t>
-  </si>
-  <si>
-    <t>(0.756)</t>
-  </si>
-  <si>
-    <t>20.766</t>
-  </si>
-  <si>
-    <t>(4.599)</t>
-  </si>
-  <si>
-    <t>41.104</t>
-  </si>
-  <si>
-    <t>(16.114)</t>
-  </si>
-  <si>
-    <t>2.800</t>
-  </si>
-  <si>
-    <t>(1.731)</t>
-  </si>
-  <si>
-    <t>6.767</t>
-  </si>
-  <si>
-    <t>(0.804)</t>
-  </si>
-  <si>
-    <t>1.169</t>
-  </si>
-  <si>
-    <t>(0.204)</t>
-  </si>
-  <si>
-    <t>10.992</t>
-  </si>
-  <si>
-    <t>(10.411)</t>
-  </si>
-  <si>
-    <t>50.566</t>
-  </si>
-  <si>
-    <t>(19.942)</t>
-  </si>
-  <si>
-    <t>31.419</t>
-  </si>
-  <si>
-    <t>(11.867)</t>
+    <t>1.622</t>
+  </si>
+  <si>
+    <t>(0.345)</t>
+  </si>
+  <si>
+    <t>7.023</t>
+  </si>
+  <si>
+    <t>(0.782)</t>
+  </si>
+  <si>
+    <t>17.193</t>
+  </si>
+  <si>
+    <t>(2.490)</t>
+  </si>
+  <si>
+    <t>21.741</t>
+  </si>
+  <si>
+    <t>(2.972)</t>
+  </si>
+  <si>
+    <t>1.113</t>
+  </si>
+  <si>
+    <t>(0.159)</t>
+  </si>
+  <si>
+    <t>7.070</t>
+  </si>
+  <si>
+    <t>(0.827)</t>
+  </si>
+  <si>
+    <t>1.210</t>
+  </si>
+  <si>
+    <t>(0.212)</t>
+  </si>
+  <si>
+    <t>0.602</t>
+  </si>
+  <si>
+    <t>(0.103)</t>
+  </si>
+  <si>
+    <t>26.927</t>
+  </si>
+  <si>
+    <t>(3.211)</t>
+  </si>
+  <si>
+    <t>17.031</t>
+  </si>
+  <si>
+    <t>(2.945)</t>
   </si>
   <si>
     <t>24</t>
@@ -195,7 +195,7 @@
     <t>(8.108)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -207,34 +207,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-4.007</t>
-  </si>
-  <si>
-    <t>-0.997</t>
-  </si>
-  <si>
-    <t>23.544**</t>
-  </si>
-  <si>
-    <t>8.344</t>
-  </si>
-  <si>
-    <t>-1.429</t>
-  </si>
-  <si>
-    <t>-1.517</t>
-  </si>
-  <si>
-    <t>0.823*</t>
-  </si>
-  <si>
-    <t>-10.587</t>
-  </si>
-  <si>
-    <t>10.400</t>
-  </si>
-  <si>
-    <t>7.146</t>
+    <t>-0.252</t>
+  </si>
+  <si>
+    <t>-1.232</t>
+  </si>
+  <si>
+    <t>27.117***</t>
+  </si>
+  <si>
+    <t>27.707***</t>
+  </si>
+  <si>
+    <t>0.258</t>
+  </si>
+  <si>
+    <t>-1.820</t>
+  </si>
+  <si>
+    <t>0.782</t>
+  </si>
+  <si>
+    <t>-0.197</t>
+  </si>
+  <si>
+    <t>34.039***</t>
+  </si>
+  <si>
+    <t>21.534***</t>
   </si>
 </sst>
 </file>
